--- a/ZCloud-财务分析-002-20261020/cno-insurance-benefits-q1-2025/targets/answer.xlsx
+++ b/ZCloud-财务分析-002-20261020/cno-insurance-benefits-q1-2025/targets/answer.xlsx
@@ -1,25 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results'!$A$1:$D$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Results'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Results'!$A$1:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Analysis'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Analysis'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Analysis'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$1:$B$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Summary'!$A$1:$B$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,16 +39,37 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="0017324D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0017324D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F6FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +77,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="hair">
+        <color rgb="00D7E3EF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,75 +475,95 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="113" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="31" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>source_note</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="180" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Change in insurance policy benefits, first quarter of 2025 versus fourth quarter of 2024</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>61.7</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>USD millions</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CNO filings: 10-K 2024, 10-Q Q3 2024, 10-Q Q1 2025, 10-Q Q2 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>CNO_2024-12-31_10K.xlsx | worksheet/table T050!G15: FY 2024 = 2,471.9.
+CNO_2024-09-30_10Q.xlsx | worksheet/table T010!S19: 9M 2024 = 1,926.4.
+CNO_2025-03-31_10Q.xlsx | worksheet/table T010!G19: Q1 2025 = 580.1.
+CNO_2025-06-30_10Q.xlsx | worksheet/table T016!N14: 9M adjustment +15.6; T016!N24: FY adjustment -21.6; worksheet Text!A131: cumulative embedded-derivative overstatement 21.6 at December 31, 2024 and 31.7 at March 31, 2025.
+Revision basis: the 21.6 and 31.7 embedded-derivative errors are cumulative balances, not separate quarterly expenses. Convert the cumulative error to the quarter's adjustment: Q1 reduction = 31.7 - 21.6 = 10.1.
+Revised Q4 = (2,471.9 - 21.6) - (1,926.4 + 15.6) = 508.3. Revised Q1 = 580.1 - 10.1 = 570.0.
+Change = 570.0 - 508.3 = 61.7 USD millions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="180" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Percentage change in insurance policy benefits, first quarter of 2025 versus fourth quarter of 2024</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="5" t="n">
         <v>12.13850088530396</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CNO filings: 10-K 2024, 10-Q Q3 2024, 10-Q Q1 2025, 10-Q Q2 2025</t>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>CNO_2024-12-31_10K.xlsx | worksheet/table T050!G15: FY 2024 = 2,471.9.
+CNO_2024-09-30_10Q.xlsx | worksheet/table T010!S19: 9M 2024 = 1,926.4.
+CNO_2025-03-31_10Q.xlsx | worksheet/table T010!G19: Q1 2025 = 580.1.
+CNO_2025-06-30_10Q.xlsx | worksheet/table T016!N14: 9M adjustment +15.6; T016!N24: FY adjustment -21.6; worksheet Text!A131: cumulative embedded-derivative overstatement 21.6 at December 31, 2024 and 31.7 at March 31, 2025.
+Revision basis: the 21.6 and 31.7 embedded-derivative errors are cumulative balances, not separate quarterly expenses. Convert the cumulative error to the quarter's adjustment: Q1 reduction = 31.7 - 21.6 = 10.1.
+Revised Q4 = (2,471.9 - 21.6) - (1,926.4 + 15.6) = 508.3. Revised Q1 = 580.1 - 10.1 = 570.0.
+Percentage change = (570.0 - 508.3) / 508.3 * 100 = 12.1385008853...%; displayed to two decimals: 12.14 percent.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:D3"/>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.15" footer="0.15"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -489,105 +571,115 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="78" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="31" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>period</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source_document</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>source_page</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Fourth quarter of 2024</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Insurance policy benefits</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>508.3</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>USD millions</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>CNO_2024-12-31_10K.xlsx; CNO_2024-09-30_10Q.xlsx; CNO_2025-06-30_10Q.xlsx</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>T050; T010; T016, Text</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>CNO_2024-12-31_10K.xlsx T050!G15; CNO_2024-09-30_10Q.xlsx T010!S19; CNO_2025-06-30_10Q.xlsx T016!N14 (+15.6), T016!N24 (-21.6), Text!A131. Revised Q4 = (2,471.9 - 21.6) - (1,926.4 + 15.6) = 508.3 USD millions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>First quarter of 2025</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Insurance policy benefits</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>570</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>USD millions</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>CNO_2025-03-31_10Q.xlsx; CNO_2025-06-30_10Q.xlsx</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>T010; Text</t>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>CNO_2025-03-31_10Q.xlsx T010!G19; CNO_2025-06-30_10Q.xlsx Text!A131 (cumulative errors 31.7 at March 31, 2025 and 21.6 at December 31, 2024), T016!N24 (2024 correction). Quarter-only adjustment = -(31.7 - 21.6) = -10.1. Revised Q1 = 580.1 - 10.1 = 570.0 USD millions.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:F3"/>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.15" footer="0.15"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -595,44 +687,50 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="31" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>quarter</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>insurance_policy_benefits</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Fourth quarter of 2024</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>508.3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>First quarter of 2025</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>570</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:B3"/>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.15" footer="0.15"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>